--- a/tests/fixtures/07_timesheet/data-export-control.xlsx
+++ b/tests/fixtures/07_timesheet/data-export-control.xlsx
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -561,201 +561,202 @@
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>table:</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>HEADER</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>day.name</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>day.hours</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>day.task</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="n"/>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="6" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Monday</t>
         </is>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E6" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Architecture review</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="7" t="n"/>
-      <c r="B6" s="7" t="n"/>
-      <c r="C6" s="8" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="7" t="n"/>
+      <c r="B7" s="7" t="n"/>
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E7" s="7" t="n">
         <v>7.5</v>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Engine development</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E8" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>Engine development</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="n"/>
-      <c r="C8" s="8" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="7" t="n"/>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>Thursday</t>
         </is>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E9" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="F8" s="7" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Code review</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="n"/>
-      <c r="C9" s="6" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="5" t="n"/>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Friday</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E10" s="5" t="n">
         <v>7.5</v>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="7" t="n"/>
-      <c r="C10" s="8" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="7" t="n"/>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>Saturday</t>
         </is>
       </c>
-      <c r="E10" s="7" t="n">
+      <c r="E11" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="7" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="n"/>
-      <c r="C11" s="6" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="5" t="n"/>
+      <c r="B12" s="5" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>DATA</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Sunday</t>
         </is>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>'-</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="9" t="n"/>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="10" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>FOOTER</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="n">
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n">
         <v>37</v>
       </c>
     </row>
